--- a/data/trans_dic/IP2005-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen los dientes sanos</t>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,77; 89,5</t>
+          <t>76,75; 89,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,08; 92,73</t>
+          <t>81,45; 92,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,8; 97,09</t>
+          <t>85,22; 96,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,66; 96,1</t>
+          <t>81,9; 96,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,24; 87,67</t>
+          <t>74,33; 88,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,52; 89,95</t>
+          <t>77,06; 90,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,7; 90,12</t>
+          <t>75,63; 90,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,85; 89,56</t>
+          <t>69,02; 89,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,01; 87,16</t>
+          <t>78,09; 87,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,58; 90,26</t>
+          <t>81,04; 90,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,28; 91,91</t>
+          <t>82,27; 91,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,72; 90,92</t>
+          <t>78,2; 90,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,9; 90,16</t>
+          <t>84,71; 90,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,54; 91,64</t>
+          <t>87,0; 91,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,15; 94,28</t>
+          <t>89,83; 94,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,29; 91,7</t>
+          <t>86,18; 91,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,22; 91,62</t>
+          <t>86,94; 91,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,06; 92,43</t>
+          <t>87,4; 92,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,92; 93,52</t>
+          <t>88,83; 93,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,26; 91,62</t>
+          <t>86,51; 91,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,91; 90,24</t>
+          <t>86,7; 90,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88,16; 91,39</t>
+          <t>87,93; 91,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,31; 93,38</t>
+          <t>90,23; 93,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,25; 91,17</t>
+          <t>87,19; 90,96</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,14; 97,04</t>
+          <t>90,93; 96,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,7; 96,99</t>
+          <t>90,64; 96,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,29; 97,72</t>
+          <t>92,15; 97,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,48; 87,6</t>
+          <t>77,66; 87,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,5; 94,33</t>
+          <t>86,14; 94,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,26; 98,25</t>
+          <t>92,91; 98,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,02; 96,34</t>
+          <t>90,28; 96,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,79; 91,51</t>
+          <t>81,88; 90,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,2; 95,07</t>
+          <t>90,17; 94,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92,92; 96,92</t>
+          <t>93,02; 97,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,15; 96,5</t>
+          <t>92,19; 96,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81,8; 88,41</t>
+          <t>81,88; 88,35</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,8; 90,72</t>
+          <t>86,87; 90,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,31; 92,24</t>
+          <t>88,19; 92,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,3; 94,61</t>
+          <t>91,45; 94,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,36; 90,05</t>
+          <t>85,45; 90,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,83; 90,76</t>
+          <t>86,86; 90,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,45</t>
+          <t>88,95; 92,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,35; 92,87</t>
+          <t>89,16; 92,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,67; 90,08</t>
+          <t>85,44; 90,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,3; 90,27</t>
+          <t>87,47; 90,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,26; 91,85</t>
+          <t>89,16; 91,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,9; 93,33</t>
+          <t>90,94; 93,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,3; 89,51</t>
+          <t>86,2; 89,51</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>71453</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77918</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51267</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48572</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66529</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69643</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55853</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>48222</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>137982</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>147561</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>107120</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96794</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>65164; 76298</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>72294; 82249</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>47061; 53499</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43978; 51681</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>60516; 71769</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>63668; 74759</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>50428; 60133</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>41274; 53246</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>129874; 145403</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>138888; 154660</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>100288; 112113</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>88757; 102559</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>342239</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>372951</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>405736</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>404227</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>402783</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>415455</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>421421</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>450449</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>745022</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>788407</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>827158</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>854677</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>331397; 352351</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>362998; 383390</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>394384; 413845</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>391145; 416338</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>391292; 412645</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>402303; 425067</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>410147; 430310</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>436786; 461900</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>729422; 759442</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>771642; 802508</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>812759; 840355</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>835953; 872081</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>151349</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>145620</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154934</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122335</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>133133</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>150234</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>159336</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>158419</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>284483</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>295855</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>314271</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>280755</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>145405; 154759</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139886; 149470</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149375; 158439</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>114573; 129086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>125808; 137620</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>144952; 153309</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>153243; 163785</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>149077; 165135</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>275884; 290345</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>288687; 301095</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>305923; 319675</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>269883; 291206</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1632</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>565042</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>596489</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>611937</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>575134</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>635333</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>657092</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1167486</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1231822</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1248548</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1232226</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>552531; 576424</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>582311; 608271</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>600248; 621850</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>559792; 590033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>588504; 614499</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>621739; 647056</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>622476; 648463</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>638014; 673197</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1149037; 1184522</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1211875; 1248490</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1231855; 1266165</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1208371; 1254796</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2005-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,75; 89,87</t>
+          <t>76,89; 89,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,45; 92,67</t>
+          <t>81,69; 92,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,22; 96,87</t>
+          <t>84,99; 97,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,9; 96,24</t>
+          <t>81,15; 96,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,33; 88,15</t>
+          <t>73,86; 87,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,06; 90,48</t>
+          <t>76,5; 90,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,63; 90,19</t>
+          <t>75,1; 90,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,02; 89,04</t>
+          <t>69,01; 88,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,09; 87,43</t>
+          <t>77,99; 87,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,04; 90,24</t>
+          <t>81,59; 90,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,27; 91,97</t>
+          <t>82,38; 91,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,2; 90,36</t>
+          <t>77,71; 90,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,71; 90,06</t>
+          <t>84,52; 89,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,0; 91,89</t>
+          <t>86,56; 91,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,83; 94,26</t>
+          <t>90,21; 94,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,18; 91,73</t>
+          <t>86,46; 91,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,94; 91,68</t>
+          <t>87,18; 91,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,4; 92,34</t>
+          <t>87,63; 92,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,83; 93,19</t>
+          <t>88,81; 93,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,51; 91,49</t>
+          <t>86,0; 91,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,7; 90,27</t>
+          <t>86,88; 90,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,93; 91,45</t>
+          <t>87,84; 91,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,23; 93,29</t>
+          <t>90,18; 93,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,19; 90,96</t>
+          <t>87,2; 90,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,93; 96,78</t>
+          <t>91,42; 97,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,64; 96,85</t>
+          <t>90,76; 96,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,15; 97,74</t>
+          <t>91,89; 97,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,66; 87,49</t>
+          <t>77,61; 87,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,14; 94,23</t>
+          <t>86,74; 94,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,91; 98,26</t>
+          <t>92,63; 98,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,28; 96,49</t>
+          <t>90,17; 96,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,88; 90,69</t>
+          <t>81,76; 90,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,17; 94,9</t>
+          <t>90,28; 94,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93,02; 97,02</t>
+          <t>93,15; 96,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,19; 96,33</t>
+          <t>92,36; 96,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81,88; 88,35</t>
+          <t>81,43; 87,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,87; 90,63</t>
+          <t>86,62; 90,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,19; 92,12</t>
+          <t>88,22; 92,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,45; 94,74</t>
+          <t>91,5; 94,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,45; 90,07</t>
+          <t>85,5; 90,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,86; 90,7</t>
+          <t>86,95; 90,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,58</t>
+          <t>89,01; 92,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,16; 92,88</t>
+          <t>89,27; 92,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,15</t>
+          <t>85,44; 90,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,47; 90,18</t>
+          <t>87,51; 90,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,16; 91,85</t>
+          <t>89,15; 91,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,94; 93,48</t>
+          <t>90,8; 93,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,2; 89,51</t>
+          <t>86,34; 89,68</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65164; 76298</t>
+          <t>65283; 76123</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72294; 82249</t>
+          <t>72510; 82084</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47061; 53499</t>
+          <t>46938; 53787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43978; 51681</t>
+          <t>43577; 51836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60516; 71769</t>
+          <t>60137; 71541</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63668; 74759</t>
+          <t>63207; 75049</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50428; 60133</t>
+          <t>50075; 60077</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41274; 53246</t>
+          <t>41270; 53203</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129874; 145403</t>
+          <t>129717; 145009</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>138888; 154660</t>
+          <t>139832; 154417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100288; 112113</t>
+          <t>100417; 111974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88757; 102559</t>
+          <t>88207; 103230</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>331397; 352351</t>
+          <t>330679; 352059</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>362998; 383390</t>
+          <t>361134; 382760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>394384; 413845</t>
+          <t>396064; 414450</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>391145; 416338</t>
+          <t>392405; 415980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>391292; 412645</t>
+          <t>392378; 413568</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>402303; 425067</t>
+          <t>403351; 424909</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>410147; 430310</t>
+          <t>410084; 431129</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>436786; 461900</t>
+          <t>434200; 462246</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>729422; 759442</t>
+          <t>730899; 759286</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>771642; 802508</t>
+          <t>770852; 801395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>812759; 840355</t>
+          <t>812302; 840334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>835953; 872081</t>
+          <t>836015; 872279</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>145405; 154759</t>
+          <t>146192; 155390</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>139886; 149470</t>
+          <t>140066; 149342</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149375; 158439</t>
+          <t>148963; 158386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114573; 129086</t>
+          <t>114511; 129072</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>125808; 137620</t>
+          <t>126687; 138401</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>144952; 153309</t>
+          <t>144528; 153320</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>153243; 163785</t>
+          <t>153055; 163582</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>149077; 165135</t>
+          <t>148861; 165478</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>275884; 290345</t>
+          <t>276219; 290458</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>288687; 301095</t>
+          <t>289082; 300988</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>305923; 319675</t>
+          <t>306493; 320207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>269883; 291206</t>
+          <t>268412; 289760</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>552531; 576424</t>
+          <t>550920; 577113</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>582311; 608271</t>
+          <t>582533; 607939</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>600248; 621850</t>
+          <t>600600; 621485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>559792; 590033</t>
+          <t>560137; 589932</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>588504; 614499</t>
+          <t>589137; 615367</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>621739; 647056</t>
+          <t>622122; 646549</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>622476; 648463</t>
+          <t>623220; 648223</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>638014; 673197</t>
+          <t>638033; 672062</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1149037; 1184522</t>
+          <t>1149480; 1184919</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1211875; 1248490</t>
+          <t>1211836; 1248887</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1231855; 1266165</t>
+          <t>1229970; 1263683</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1208371; 1254796</t>
+          <t>1210300; 1257116</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2005-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>79,15%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>84,16%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>87,79%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>92,83%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,77%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>83,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,89; 89,66</t>
+          <t>74,24; 87,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,69; 92,48</t>
+          <t>76,52; 89,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,99; 97,39</t>
+          <t>75,7; 90,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,15; 96,53</t>
+          <t>67,4; 88,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,86; 87,87</t>
+          <t>76,77; 89,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,5; 90,83</t>
+          <t>81,08; 92,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,1; 90,11</t>
+          <t>85,8; 97,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,01; 88,96</t>
+          <t>78,34; 95,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,99; 87,19</t>
+          <t>78,01; 87,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,59; 90,1</t>
+          <t>81,58; 90,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,38; 91,86</t>
+          <t>82,28; 91,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,71; 90,95</t>
+          <t>76,58; 89,47</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89,27%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>87,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>89,39%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>92,41%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>89,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,52; 89,99</t>
+          <t>87,22; 91,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,56; 91,74</t>
+          <t>88,06; 92,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,21; 94,4</t>
+          <t>88,92; 93,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,46; 91,65</t>
+          <t>86,34; 91,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,18; 91,89</t>
+          <t>84,9; 90,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,63; 92,31</t>
+          <t>86,54; 91,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,81; 93,37</t>
+          <t>90,15; 94,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,0; 91,56</t>
+          <t>85,48; 90,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,88; 90,25</t>
+          <t>86,91; 90,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,84; 91,32</t>
+          <t>88,16; 91,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,18; 93,29</t>
+          <t>90,31; 93,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,2; 90,98</t>
+          <t>86,97; 90,69</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>94,65%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>94,36%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>95,58%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82,92%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,87%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,42; 97,18</t>
+          <t>86,5; 94,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,76; 96,77</t>
+          <t>93,26; 98,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,89; 97,71</t>
+          <t>90,02; 96,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,61; 87,48</t>
+          <t>81,83; 91,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,74; 94,76</t>
+          <t>91,14; 97,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,63; 98,27</t>
+          <t>90,7; 96,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,17; 96,37</t>
+          <t>92,29; 97,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,76; 90,88</t>
+          <t>77,79; 87,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,28; 94,93</t>
+          <t>90,2; 95,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93,15; 96,98</t>
+          <t>92,92; 96,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,36; 96,49</t>
+          <t>92,15; 96,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81,43; 87,91</t>
+          <t>82,05; 88,55</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90,9%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>88,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,62; 90,74</t>
+          <t>86,83; 90,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,22; 92,07</t>
+          <t>88,95; 92,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,5; 94,68</t>
+          <t>89,35; 92,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,5; 90,05</t>
+          <t>85,52; 90,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,95; 90,82</t>
+          <t>86,8; 90,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,01; 92,5</t>
+          <t>88,31; 92,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,27; 92,85</t>
+          <t>91,3; 94,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,0</t>
+          <t>84,65; 89,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,51; 90,21</t>
+          <t>87,3; 90,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,15; 91,88</t>
+          <t>89,26; 91,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,8; 93,29</t>
+          <t>90,9; 93,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,34; 89,68</t>
+          <t>85,92; 89,15</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>66529</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69643</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55853</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43479</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>71453</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>77918</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>51267</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48572</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>66529</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69643</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55853</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48222</t>
+          <t>40665</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96794</t>
+          <t>84144</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65283; 76123</t>
+          <t>60442; 71380</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72510; 82084</t>
+          <t>63228; 74321</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46938; 53787</t>
+          <t>50474; 60090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43577; 51836</t>
+          <t>37025; 48735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60137; 71541</t>
+          <t>65183; 75986</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63207; 75049</t>
+          <t>71963; 82308</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50075; 60077</t>
+          <t>47384; 53617</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41270; 53203</t>
+          <t>35960; 43608</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129717; 145009</t>
+          <t>129749; 144963</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139832; 154417</t>
+          <t>139823; 154697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100417; 111974</t>
+          <t>100294; 112037</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88207; 103230</t>
+          <t>77217; 90220</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>516</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>543</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>557</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>402783</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>415455</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>421421</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>416210</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>342239</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>372951</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>405736</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>404227</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>402783</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>415455</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>421421</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>450449</t>
+          <t>376936</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>854677</t>
+          <t>793146</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>330679; 352059</t>
+          <t>392532; 412350</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>361134; 382760</t>
+          <t>405334; 425455</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>396064; 414450</t>
+          <t>410599; 431806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>392405; 415980</t>
+          <t>402560; 427801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>392378; 413568</t>
+          <t>332156; 352736</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>403351; 424909</t>
+          <t>361062; 382348</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>410084; 431129</t>
+          <t>395805; 413928</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>434200; 462246</t>
+          <t>364533; 387849</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>730899; 759286</t>
+          <t>731192; 759173</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>770852; 801395</t>
+          <t>773594; 801937</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>812302; 840334</t>
+          <t>813478; 841153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>836015; 872279</t>
+          <t>776401; 809646</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>186</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>133133</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>150234</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159336</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145766</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>151349</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>145620</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>154934</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>122335</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>133133</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>150234</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>159336</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>158419</t>
+          <t>123490</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>280755</t>
+          <t>269256</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>146192; 155390</t>
+          <t>126335; 137766</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>140066; 149342</t>
+          <t>145503; 153298</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148963; 158386</t>
+          <t>152801; 163525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114511; 129072</t>
+          <t>136985; 152921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>126687; 138401</t>
+          <t>145731; 155166</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>144528; 153320</t>
+          <t>139969; 149682</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>153055; 163582</t>
+          <t>149600; 158413</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>148861; 165478</t>
+          <t>115367; 130305</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>276219; 290458</t>
+          <t>275973; 290890</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>289082; 300988</t>
+          <t>288360; 300780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>306493; 320207</t>
+          <t>305786; 320231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>268412; 289760</t>
+          <t>259026; 279550</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>861</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>803</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>635333</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>605456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>565042</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>596489</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>611937</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>575134</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>602445</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>635333</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>636612</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>657092</t>
+          <t>541089</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1232226</t>
+          <t>1146545</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>550920; 577113</t>
+          <t>588309; 614921</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>582533; 607939</t>
+          <t>621686; 646164</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>600600; 621485</t>
+          <t>623795; 648383</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>560137; 589932</t>
+          <t>588897; 619965</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>589137; 615367</t>
+          <t>552078; 577011</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>622122; 646549</t>
+          <t>583154; 609046</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>623220; 648223</t>
+          <t>599300; 621013</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>638033; 672062</t>
+          <t>525394; 555046</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1149480; 1184919</t>
+          <t>1146804; 1185783</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1211836; 1248887</t>
+          <t>1213248; 1248464</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1229970; 1263683</t>
+          <t>1231256; 1264212</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1210300; 1257116</t>
+          <t>1124878; 1167151</t>
         </is>
       </c>
     </row>
